--- a/data/processed/sam_auto_dashboard_2024_refresh/custom_table_output/occ_change_by_education_2024_2030/training/occ_change_by_training_2024_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/custom_table_output/occ_change_by_education_2024_2030/training/occ_change_by_training_2024_2030.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasilauskas\GitHub-Local\EV-Transition-MI-Mobility\data\processed\sam_auto_dashboard_2024_refresh\custom_table_output\occ_change_by_education_2024_2030\training\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265A6F0E-4D3F-4A25-9354-44F97A8311D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="segments" sheetId="1" r:id="rId1"/>
     <sheet name="stages" sheetId="2" r:id="rId2"/>
     <sheet name="total" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -126,8 +132,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,13 +196,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -234,7 +248,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -268,6 +282,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -302,9 +317,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -477,11 +493,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -518,16 +538,16 @@
         <v>1010.223883424442</v>
       </c>
       <c r="E2">
-        <v>966.3535418545209</v>
+        <v>966.35354185452093</v>
       </c>
       <c r="F2">
-        <v>-43.87034156992115</v>
+        <v>-43.870341569921152</v>
       </c>
       <c r="G2">
-        <v>-0.04342635557299449</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>-4.3426355572994492E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -541,16 +561,16 @@
         <v>1291.804296900388</v>
       </c>
       <c r="E3">
-        <v>1184.465269539763</v>
+        <v>1184.4652695397631</v>
       </c>
       <c r="F3">
         <v>-107.3390273606251</v>
       </c>
       <c r="G3">
-        <v>-0.08309232878244718</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>-8.3092328782447183E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -561,19 +581,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>3916.133750496152</v>
+        <v>3916.1337504961521</v>
       </c>
       <c r="E4">
-        <v>3600.507659598101</v>
+        <v>3600.5076595981009</v>
       </c>
       <c r="F4">
-        <v>-315.6260908980503</v>
+        <v>-315.62609089805028</v>
       </c>
       <c r="G4">
-        <v>-0.08059635114813489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>-8.059635114813489E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -584,19 +604,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>218.5840051267336</v>
+        <v>218.58400512673359</v>
       </c>
       <c r="E5">
-        <v>220.2384235357682</v>
+        <v>220.23842353576819</v>
       </c>
       <c r="F5">
         <v>1.654418409034605</v>
       </c>
       <c r="G5">
-        <v>0.007568799043989443</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>7.5687990439894434E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -613,13 +633,13 @@
         <v>108.2376548877113</v>
       </c>
       <c r="F6">
-        <v>-4.097482194126513</v>
+        <v>-4.0974821941265134</v>
       </c>
       <c r="G6">
-        <v>-0.03647551692700955</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>-3.6475516927009552E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -630,19 +650,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>489.1621371690559</v>
+        <v>489.16213716905588</v>
       </c>
       <c r="E7">
-        <v>473.5976251788956</v>
+        <v>473.59762517889561</v>
       </c>
       <c r="F7">
         <v>-15.56451199016033</v>
       </c>
       <c r="G7">
-        <v>-0.03181871777778496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>-3.1818717777784958E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -653,19 +673,19 @@
         <v>17</v>
       </c>
       <c r="D8">
-        <v>632.3410114307957</v>
+        <v>632.34101143079567</v>
       </c>
       <c r="E8">
-        <v>548.0217205588411</v>
+        <v>548.02172055884114</v>
       </c>
       <c r="F8">
-        <v>-84.31929087195454</v>
+        <v>-84.319290871954536</v>
       </c>
       <c r="G8">
-        <v>-0.1333446500349006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>-0.13334465003490059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3</v>
       </c>
@@ -676,10 +696,10 @@
         <v>18</v>
       </c>
       <c r="D9">
-        <v>879.6426941190805</v>
+        <v>879.64269411908049</v>
       </c>
       <c r="E9">
-        <v>734.5025565307475</v>
+        <v>734.50255653074748</v>
       </c>
       <c r="F9">
         <v>-145.140137588333</v>
@@ -688,7 +708,7 @@
         <v>-0.164998968966239</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
@@ -699,19 +719,19 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>3471.614760776018</v>
+        <v>3471.6147607760181</v>
       </c>
       <c r="E10">
-        <v>2843.076555972017</v>
+        <v>2843.0765559720171</v>
       </c>
       <c r="F10">
-        <v>-628.5382048040005</v>
+        <v>-628.53820480400054</v>
       </c>
       <c r="G10">
-        <v>-0.1810506775998101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>-0.18105067759981011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>4</v>
       </c>
@@ -722,19 +742,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>754.6878089099919</v>
+        <v>754.68780890999187</v>
       </c>
       <c r="E11">
-        <v>753.0092206859061</v>
+        <v>753.00922068590614</v>
       </c>
       <c r="F11">
-        <v>-1.678588224085729</v>
+        <v>-1.6785882240857291</v>
       </c>
       <c r="G11">
-        <v>-0.002224215369942363</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>-2.2242153699423631E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>4</v>
       </c>
@@ -745,19 +765,19 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>701.5769755928326</v>
+        <v>701.57697559283258</v>
       </c>
       <c r="E12">
-        <v>654.7733497418861</v>
+        <v>654.77334974188614</v>
       </c>
       <c r="F12">
-        <v>-46.80362585094645</v>
+        <v>-46.803625850946453</v>
       </c>
       <c r="G12">
-        <v>-0.06671203229181998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>-6.6712032291819975E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -768,19 +788,19 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>2966.497028666647</v>
+        <v>2966.4970286666471</v>
       </c>
       <c r="E13">
         <v>2799.589618938297</v>
       </c>
       <c r="F13">
-        <v>-166.9074097283496</v>
+        <v>-166.90740972834959</v>
       </c>
       <c r="G13">
-        <v>-0.05626414188702884</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>-5.6264141887028843E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
@@ -794,16 +814,16 @@
         <v>800.3180821149183</v>
       </c>
       <c r="E14">
-        <v>788.8613888098137</v>
+        <v>788.86138880981366</v>
       </c>
       <c r="F14">
         <v>-11.45669330510464</v>
       </c>
       <c r="G14">
-        <v>-0.01431517488000422</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>-1.431517488000422E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>5</v>
       </c>
@@ -817,16 +837,16 @@
         <v>252.5393948137008</v>
       </c>
       <c r="E15">
-        <v>242.783300535245</v>
+        <v>242.78330053524499</v>
       </c>
       <c r="F15">
-        <v>-9.756094278455834</v>
+        <v>-9.7560942784558335</v>
       </c>
       <c r="G15">
-        <v>-0.03863196981862152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>-3.863196981862152E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>5</v>
       </c>
@@ -837,19 +857,19 @@
         <v>19</v>
       </c>
       <c r="D16">
-        <v>907.6778248376519</v>
+        <v>907.67782483765188</v>
       </c>
       <c r="E16">
-        <v>890.1403797579462</v>
+        <v>890.14037975794622</v>
       </c>
       <c r="F16">
-        <v>-17.53744507970566</v>
+        <v>-17.537445079705659</v>
       </c>
       <c r="G16">
-        <v>-0.01932122235424494</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>-1.9321222354244941E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>6</v>
       </c>
@@ -860,19 +880,19 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>6.335405448861793</v>
+        <v>6.3354054488617928</v>
       </c>
       <c r="E17">
-        <v>6.495547905034462</v>
+        <v>6.4955479050344618</v>
       </c>
       <c r="F17">
-        <v>0.160142456172669</v>
+        <v>0.16014245617266901</v>
       </c>
       <c r="G17">
-        <v>0.0252773808188456</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>2.5277380818845601E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>6</v>
       </c>
@@ -883,19 +903,19 @@
         <v>18</v>
       </c>
       <c r="D18">
-        <v>0.6607478075499962</v>
+        <v>0.66074780754999618</v>
       </c>
       <c r="E18">
         <v>0.6452080125438211</v>
       </c>
       <c r="F18">
-        <v>-0.01553979500617508</v>
+        <v>-1.553979500617508E-2</v>
       </c>
       <c r="G18">
-        <v>-0.02351849651048482</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>-2.3518496510484821E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6</v>
       </c>
@@ -906,19 +926,19 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>1.864201330669384</v>
+        <v>1.8642013306693841</v>
       </c>
       <c r="E19">
         <v>1.855386410090393</v>
       </c>
       <c r="F19">
-        <v>-0.008814920578991803</v>
+        <v>-8.8149205789918028E-3</v>
       </c>
       <c r="G19">
-        <v>-0.004728523917439005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>-4.7285239174390051E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>7</v>
       </c>
@@ -929,19 +949,19 @@
         <v>17</v>
       </c>
       <c r="D20">
-        <v>28420.73848797222</v>
+        <v>28420.738487972219</v>
       </c>
       <c r="E20">
-        <v>29477.97771335054</v>
+        <v>29477.977713350541</v>
       </c>
       <c r="F20">
         <v>1057.239225378318</v>
       </c>
       <c r="G20">
-        <v>0.03719956910429145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>3.7199569104291452E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7</v>
       </c>
@@ -952,19 +972,19 @@
         <v>18</v>
       </c>
       <c r="D21">
-        <v>19251.15945017174</v>
+        <v>19251.159450171741</v>
       </c>
       <c r="E21">
         <v>18859.45959321535</v>
       </c>
       <c r="F21">
-        <v>-391.6998569563912</v>
+        <v>-391.69985695639122</v>
       </c>
       <c r="G21">
-        <v>-0.02034681900434297</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>-2.0346819004342969E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
@@ -984,10 +1004,10 @@
         <v>1225.472631578057</v>
       </c>
       <c r="G22">
-        <v>0.009771721826473095</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>9.7717218264730954E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
@@ -1001,16 +1021,16 @@
         <v>19646.96893063571</v>
       </c>
       <c r="E23">
-        <v>20716.31565468315</v>
+        <v>20716.315654683149</v>
       </c>
       <c r="F23">
-        <v>1069.346724047435</v>
+        <v>1069.3467240474349</v>
       </c>
       <c r="G23">
-        <v>0.05442807630137755</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>5.4428076301377547E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -1021,19 +1041,19 @@
         <v>18</v>
       </c>
       <c r="D24">
-        <v>60774.34609826608</v>
+        <v>60774.346098266084</v>
       </c>
       <c r="E24">
         <v>60014.07059865597</v>
       </c>
       <c r="F24">
-        <v>-760.2754996101139</v>
+        <v>-760.27549961011391</v>
       </c>
       <c r="G24">
-        <v>-0.01250980962231702</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>-1.2509809622317019E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>8</v>
       </c>
@@ -1044,19 +1064,19 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>34918.68497109821</v>
+        <v>34918.684971098213</v>
       </c>
       <c r="E25">
-        <v>36225.75974666086</v>
+        <v>36225.759746660857</v>
       </c>
       <c r="F25">
         <v>1307.074775562643</v>
       </c>
       <c r="G25">
-        <v>0.03743195875344372</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>3.7431958753443718E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9</v>
       </c>
@@ -1067,19 +1087,19 @@
         <v>17</v>
       </c>
       <c r="D26">
-        <v>6147.44206383908</v>
+        <v>6147.4420638390802</v>
       </c>
       <c r="E26">
         <v>6300.020290295166</v>
       </c>
       <c r="F26">
-        <v>152.5782264560858</v>
+        <v>152.57822645608579</v>
       </c>
       <c r="G26">
-        <v>0.02481979087750858</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>2.4819790877508581E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9</v>
       </c>
@@ -1090,19 +1110,19 @@
         <v>18</v>
       </c>
       <c r="D27">
-        <v>34734.06209007435</v>
+        <v>34734.062090074352</v>
       </c>
       <c r="E27">
-        <v>35597.97077432211</v>
+        <v>35597.970774322108</v>
       </c>
       <c r="F27">
-        <v>863.9086842477554</v>
+        <v>863.90868424775545</v>
       </c>
       <c r="G27">
-        <v>0.02487208901761672</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>2.4872089017616721E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9</v>
       </c>
@@ -1113,19 +1133,19 @@
         <v>19</v>
       </c>
       <c r="D28">
-        <v>28718.49584608657</v>
+        <v>28718.495846086571</v>
       </c>
       <c r="E28">
-        <v>29798.01293538272</v>
+        <v>29798.012935382721</v>
       </c>
       <c r="F28">
-        <v>1079.517089296154</v>
+        <v>1079.5170892961539</v>
       </c>
       <c r="G28">
-        <v>0.03758961106743543</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>3.7589611067435427E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>10</v>
       </c>
@@ -1136,19 +1156,19 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>3914.073253833027</v>
+        <v>3914.0732538330271</v>
       </c>
       <c r="E29">
         <v>3601.574161102707</v>
       </c>
       <c r="F29">
-        <v>-312.4990927303202</v>
+        <v>-312.49909273032023</v>
       </c>
       <c r="G29">
-        <v>-0.07983986820489161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>-7.9839868204891612E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>10</v>
       </c>
@@ -1159,10 +1179,10 @@
         <v>18</v>
       </c>
       <c r="D30">
-        <v>10643.88287904598</v>
+        <v>10643.882879045979</v>
       </c>
       <c r="E30">
-        <v>9488.084725005965</v>
+        <v>9488.0847250059651</v>
       </c>
       <c r="F30">
         <v>-1155.798154040016</v>
@@ -1171,7 +1191,7 @@
         <v>-0.1085880187873329</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>10</v>
       </c>
@@ -1182,16 +1202,16 @@
         <v>19</v>
       </c>
       <c r="D31">
-        <v>32331.043867121</v>
+        <v>32331.043867120999</v>
       </c>
       <c r="E31">
-        <v>28634.18811389134</v>
+        <v>28634.188113891341</v>
       </c>
       <c r="F31">
-        <v>-3696.855753229658</v>
+        <v>-3696.8557532296581</v>
       </c>
       <c r="G31">
-        <v>-0.1143438414306557</v>
+        <v>-0.11434384143065569</v>
       </c>
     </row>
   </sheetData>
@@ -1200,11 +1220,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1227,7 +1247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1238,19 +1258,19 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>3416.154791006882</v>
+        <v>3416.1547910068821</v>
       </c>
       <c r="E2">
         <v>3276.48429544485</v>
       </c>
       <c r="F2">
-        <v>-139.6704955620316</v>
+        <v>-139.67049556203159</v>
       </c>
       <c r="G2">
-        <v>-0.04088529475588107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>-4.0885294755881069E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1264,16 +1284,16 @@
         <v>3237.89849850784</v>
       </c>
       <c r="E3">
-        <v>2924.762131235353</v>
+        <v>2924.7621312353531</v>
       </c>
       <c r="F3">
-        <v>-313.136367272487</v>
+        <v>-313.13636727248701</v>
       </c>
       <c r="G3">
-        <v>-0.09670975400148997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>-9.670975400148997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1284,7 +1304,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>11751.08550194552</v>
+        <v>11751.085501945519</v>
       </c>
       <c r="E4">
         <v>10606.91183944526</v>
@@ -1293,10 +1313,10 @@
         <v>-1144.173662500265</v>
       </c>
       <c r="G4">
-        <v>-0.09736748680033298</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>-9.7367486800332984E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1307,19 +1327,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>28427.07389342108</v>
+        <v>28427.073893421079</v>
       </c>
       <c r="E5">
-        <v>29484.47326125557</v>
+        <v>29484.473261255571</v>
       </c>
       <c r="F5">
-        <v>1057.399367834492</v>
+        <v>1057.3993678344921</v>
       </c>
       <c r="G5">
-        <v>0.03719691206343991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>3.7196912063439912E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1333,16 +1353,16 @@
         <v>19251.82019797929</v>
       </c>
       <c r="E6">
-        <v>18860.10480122789</v>
+        <v>18860.104801227892</v>
       </c>
       <c r="F6">
-        <v>-391.7153967513987</v>
+        <v>-391.71539675139871</v>
       </c>
       <c r="G6">
-        <v>-0.02034692786048947</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>-2.0346927860489469E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1359,13 +1379,13 @@
         <v>126637.4300798442</v>
       </c>
       <c r="F7">
-        <v>1225.463816657459</v>
+        <v>1225.4638166574589</v>
       </c>
       <c r="G7">
-        <v>0.009771506285817478</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>9.7715062858174783E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1376,19 +1396,19 @@
         <v>17</v>
       </c>
       <c r="D8">
-        <v>29708.48424830782</v>
+        <v>29708.484248307821</v>
       </c>
       <c r="E8">
-        <v>30617.91010608102</v>
+        <v>30617.910106081021</v>
       </c>
       <c r="F8">
-        <v>909.4258577731998</v>
+        <v>909.42585777319982</v>
       </c>
       <c r="G8">
-        <v>0.03061165457557802</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>3.0611654575578021E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1405,13 +1425,13 @@
         <v>105100.126097984</v>
       </c>
       <c r="F9">
-        <v>-1052.16496940238</v>
+        <v>-1052.1649694023799</v>
       </c>
       <c r="G9">
-        <v>-0.009911844189349208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>-9.9118441893492077E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1422,19 +1442,19 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>95968.22468430577</v>
+        <v>95968.224684305766</v>
       </c>
       <c r="E10">
-        <v>94657.96079593492</v>
+        <v>94657.960795934923</v>
       </c>
       <c r="F10">
-        <v>-1310.263888370842</v>
+        <v>-1310.2638883708421</v>
       </c>
       <c r="G10">
-        <v>-0.01365310124972143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>-1.365310124972143E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1445,19 +1465,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>31843.22868442796</v>
+        <v>31843.228684427959</v>
       </c>
       <c r="E11">
-        <v>32760.95755670042</v>
+        <v>32760.957556700421</v>
       </c>
       <c r="F11">
-        <v>917.7288722724588</v>
+        <v>917.72887227245883</v>
       </c>
       <c r="G11">
-        <v>0.02882022050487765</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>2.8820220504877651E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1468,19 +1488,19 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>22489.71869648713</v>
+        <v>22489.718696487129</v>
       </c>
       <c r="E12">
         <v>21784.86693246325</v>
       </c>
       <c r="F12">
-        <v>-704.8517640238861</v>
+        <v>-704.85176402388606</v>
       </c>
       <c r="G12">
-        <v>-0.03134106626838259</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>-3.1341066268382588E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1494,16 +1514,16 @@
         <v>137163.0517651322</v>
       </c>
       <c r="E13">
-        <v>137244.3419192894</v>
+        <v>137244.34191928941</v>
       </c>
       <c r="F13">
-        <v>81.29015415720642</v>
+        <v>81.290154157206416</v>
       </c>
       <c r="G13">
-        <v>0.0005926534377231677</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>5.9265343772316767E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1514,19 +1534,19 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>61551.71293273578</v>
+        <v>61551.712932735783</v>
       </c>
       <c r="E14">
-        <v>63378.86766278144</v>
+        <v>63378.867662781442</v>
       </c>
       <c r="F14">
-        <v>1827.154730045659</v>
+        <v>1827.1547300456591</v>
       </c>
       <c r="G14">
-        <v>0.02968487216663472</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>2.9684872166634721E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1540,16 +1560,16 @@
         <v>128642.0097638735</v>
       </c>
       <c r="E15">
-        <v>126884.9930304473</v>
+        <v>126884.99303044729</v>
       </c>
       <c r="F15">
         <v>-1757.016733426266</v>
       </c>
       <c r="G15">
-        <v>-0.01365818783965926</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>-1.3658187839659259E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1560,16 +1580,16 @@
         <v>19</v>
       </c>
       <c r="D16">
-        <v>233131.276449438</v>
+        <v>233131.27644943801</v>
       </c>
       <c r="E16">
-        <v>231902.3027152244</v>
+        <v>231902.30271522439</v>
       </c>
       <c r="F16">
         <v>-1228.97373421365</v>
       </c>
       <c r="G16">
-        <v>-0.005271595269973108</v>
+        <v>-5.2715952699731077E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1578,11 +1598,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1605,7 +1625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1616,19 +1636,19 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>61551.71293273578</v>
+        <v>61551.712932735783</v>
       </c>
       <c r="E2">
-        <v>63378.86766278144</v>
+        <v>63378.867662781442</v>
       </c>
       <c r="F2">
-        <v>1827.154730045659</v>
+        <v>1827.1547300456591</v>
       </c>
       <c r="G2">
-        <v>0.02968487216663472</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>2.9684872166634721E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1642,16 +1662,16 @@
         <v>128642.0097638735</v>
       </c>
       <c r="E3">
-        <v>126884.9930304473</v>
+        <v>126884.99303044729</v>
       </c>
       <c r="F3">
         <v>-1757.016733426266</v>
       </c>
       <c r="G3">
-        <v>-0.01365818783965926</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>-1.3658187839659259E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1662,16 +1682,16 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>233131.276449438</v>
+        <v>233131.27644943801</v>
       </c>
       <c r="E4">
-        <v>231902.3027152244</v>
+        <v>231902.30271522439</v>
       </c>
       <c r="F4">
         <v>-1228.97373421365</v>
       </c>
       <c r="G4">
-        <v>-0.005271595269973108</v>
+        <v>-5.2715952699731077E-3</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/sam_auto_dashboard_2024_refresh/custom_table_output/occ_change_by_education_2024_2030/training/occ_change_by_training_2024_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/custom_table_output/occ_change_by_education_2024_2030/training/occ_change_by_training_2024_2030.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasilauskas\GitHub-Local\EV-Transition-MI-Mobility\data\processed\sam_auto_dashboard_2024_refresh\custom_table_output\occ_change_by_education_2024_2030\training\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265A6F0E-4D3F-4A25-9354-44F97A8311D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="segments" sheetId="1" r:id="rId1"/>
     <sheet name="stages" sheetId="2" r:id="rId2"/>
     <sheet name="total" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="34">
   <si>
     <t>segment_id</t>
   </si>
@@ -33,10 +27,10 @@
     <t>training_group</t>
   </si>
   <si>
-    <t>employment_base_auto_adj</t>
-  </si>
-  <si>
-    <t>employment_target_auto_adj</t>
+    <t>employment_base</t>
+  </si>
+  <si>
+    <t>employment_target</t>
   </si>
   <si>
     <t>employment_change</t>
@@ -45,6 +39,15 @@
     <t>pct_change</t>
   </si>
   <si>
+    <t>share_base</t>
+  </si>
+  <si>
+    <t>share_target</t>
+  </si>
+  <si>
+    <t>share_change</t>
+  </si>
+  <si>
     <t>1. Materials &amp; Processing</t>
   </si>
   <si>
@@ -78,52 +81,40 @@
     <t>BA+</t>
   </si>
   <si>
-    <t>HS or Less - Limited Training</t>
-  </si>
-  <si>
-    <t>SC/Associate or Employer Training</t>
-  </si>
-  <si>
     <t>stage_key</t>
   </si>
   <si>
     <t>stage_label</t>
   </si>
   <si>
-    <t>employment_base</t>
-  </si>
-  <si>
-    <t>employment_target</t>
+    <t>all_segments</t>
+  </si>
+  <si>
+    <t>core_auto</t>
+  </si>
+  <si>
+    <t>downstream</t>
   </si>
   <si>
     <t>upstream</t>
   </si>
   <si>
-    <t>core_oem</t>
-  </si>
-  <si>
-    <t>downstream</t>
-  </si>
-  <si>
     <t>upstream_core</t>
   </si>
   <si>
-    <t>all_segments</t>
-  </si>
-  <si>
-    <t>Upstream (segments 1-5)</t>
-  </si>
-  <si>
-    <t>Core/OEM (segments 6-7)</t>
+    <t>All Segments (segments 1-10)</t>
+  </si>
+  <si>
+    <t>Core Automotive (segment 7)</t>
   </si>
   <si>
     <t>Downstream (segments 8-10)</t>
   </si>
   <si>
-    <t>Upstream + Core/OEM (segments 1-7)</t>
-  </si>
-  <si>
-    <t>All Segments (segments 1-10)</t>
+    <t>Upstream (segments 1-6)</t>
+  </si>
+  <si>
+    <t>Upstream + Core Automotive (segments 1-7)</t>
   </si>
   <si>
     <t>All Segments</t>
@@ -132,8 +123,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,21 +187,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -248,7 +231,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -282,7 +265,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -317,10 +299,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -493,15 +474,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,476 +500,623 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>1010.223883424442</v>
+        <v>1010.223883630546</v>
       </c>
       <c r="E2">
-        <v>966.35354185452093</v>
+        <v>966.3535420516746</v>
       </c>
       <c r="F2">
-        <v>-43.870341569921152</v>
+        <v>-43.87034157887149</v>
       </c>
       <c r="G2">
-        <v>-4.3426355572994492E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.04342635557299448</v>
+      </c>
+      <c r="H2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="I2">
+        <v>0.1680227242756013</v>
+      </c>
+      <c r="J2">
+        <v>0.09397388447319016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>1291.804296900388</v>
+        <v>1291.80429716394</v>
       </c>
       <c r="E3">
-        <v>1184.4652695397631</v>
+        <v>1184.465269781416</v>
       </c>
       <c r="F3">
-        <v>-107.3390273606251</v>
+        <v>-107.3390273825241</v>
       </c>
       <c r="G3">
-        <v>-8.3092328782447183E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.08309232878244713</v>
+      </c>
+      <c r="H3">
+        <v>0.2077469694858577</v>
+      </c>
+      <c r="I3">
+        <v>0.2059464500083204</v>
+      </c>
+      <c r="J3">
+        <v>0.2299290362390973</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>3916.1337504961521</v>
+        <v>3916.133751295115</v>
       </c>
       <c r="E4">
-        <v>3600.5076595981009</v>
+        <v>3600.507660332671</v>
       </c>
       <c r="F4">
-        <v>-315.62609089805028</v>
+        <v>-315.6260909624439</v>
       </c>
       <c r="G4">
-        <v>-8.059635114813489E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.0805963511481349</v>
+      </c>
+      <c r="H4">
+        <v>0.6297896056848274</v>
+      </c>
+      <c r="I4">
+        <v>0.6260308257160782</v>
+      </c>
+      <c r="J4">
+        <v>0.6760970792877126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>218.58400512673359</v>
+        <v>218.5840051417633</v>
       </c>
       <c r="E5">
-        <v>220.23842353576819</v>
+        <v>220.2384235509117</v>
       </c>
       <c r="F5">
-        <v>1.654418409034605</v>
+        <v>1.654418409148377</v>
       </c>
       <c r="G5">
-        <v>7.5687990439894434E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.007568799043989514</v>
+      </c>
+      <c r="H5">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="I5">
+        <v>0.2745862662578333</v>
+      </c>
+      <c r="J5">
+        <v>-0.09187346646117021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>112.3351370818378</v>
+        <v>112.3351370895619</v>
       </c>
       <c r="E6">
-        <v>108.2376548877113</v>
+        <v>108.2376548951536</v>
       </c>
       <c r="F6">
-        <v>-4.0974821941265134</v>
+        <v>-4.097482194408258</v>
       </c>
       <c r="G6">
-        <v>-3.6475516927009552E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.03647551692700959</v>
+      </c>
+      <c r="H6">
+        <v>0.136980491942324</v>
+      </c>
+      <c r="I6">
+        <v>0.1349472678153898</v>
+      </c>
+      <c r="J6">
+        <v>0.2275421325594348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>489.16213716905588</v>
+        <v>489.1621372026904</v>
       </c>
       <c r="E7">
-        <v>473.59762517889561</v>
+        <v>473.5976252114598</v>
       </c>
       <c r="F7">
-        <v>-15.56451199016033</v>
+        <v>-15.56451199123057</v>
       </c>
       <c r="G7">
-        <v>-3.1818717777784958E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.03181871777778505</v>
+      </c>
+      <c r="H7">
+        <v>0.5964800678541142</v>
+      </c>
+      <c r="I7">
+        <v>0.5904664659267769</v>
+      </c>
+      <c r="J7">
+        <v>0.8643313339017354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>632.34101143079567</v>
+        <v>632.3410114560011</v>
       </c>
       <c r="E8">
-        <v>548.02172055884114</v>
+        <v>548.0217205806855</v>
       </c>
       <c r="F8">
-        <v>-84.319290871954536</v>
+        <v>-84.31929087531557</v>
       </c>
       <c r="G8">
-        <v>-0.13334465003490059</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.1333446500349007</v>
+      </c>
+      <c r="H8">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="I8">
+        <v>0.1328344022444252</v>
+      </c>
+      <c r="J8">
+        <v>0.09827450286914928</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>879.64269411908049</v>
+        <v>879.6426941541436</v>
       </c>
       <c r="E9">
-        <v>734.50255653074748</v>
+        <v>734.5025565600253</v>
       </c>
       <c r="F9">
-        <v>-145.140137588333</v>
+        <v>-145.1401375941183</v>
       </c>
       <c r="G9">
-        <v>-0.164998968966239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.1649989689662389</v>
+      </c>
+      <c r="H9">
+        <v>0.1765075376884422</v>
+      </c>
+      <c r="I9">
+        <v>0.1780352938278989</v>
+      </c>
+      <c r="J9">
+        <v>0.1691614661408111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>3471.6147607760181</v>
+        <v>3471.614760914398</v>
       </c>
       <c r="E10">
-        <v>2843.0765559720171</v>
+        <v>2843.076556085344</v>
       </c>
       <c r="F10">
-        <v>-628.53820480400054</v>
+        <v>-628.5382048290544</v>
       </c>
       <c r="G10">
-        <v>-0.18105067759981011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.1810506775998101</v>
+      </c>
+      <c r="H10">
+        <v>0.6966080402010054</v>
+      </c>
+      <c r="I10">
+        <v>0.6891303039276759</v>
+      </c>
+      <c r="J10">
+        <v>0.7325640309900396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>754.68780890999187</v>
+        <v>754.6878086751323</v>
       </c>
       <c r="E11">
-        <v>753.00922068590614</v>
+        <v>753.0092204515689</v>
       </c>
       <c r="F11">
-        <v>-1.6785882240857291</v>
+        <v>-1.678588223563338</v>
       </c>
       <c r="G11">
-        <v>-2.2242153699423631E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.002224215369942347</v>
+      </c>
+      <c r="H11">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="I11">
+        <v>0.1789737600560029</v>
+      </c>
+      <c r="J11">
+        <v>0.007793264106436333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>701.57697559283258</v>
+        <v>701.5769753745011</v>
       </c>
       <c r="E12">
-        <v>654.77334974188614</v>
+        <v>654.7733495381201</v>
       </c>
       <c r="F12">
-        <v>-46.803625850946453</v>
+        <v>-46.803625836381</v>
       </c>
       <c r="G12">
-        <v>-6.6712032291819975E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.06671203229181982</v>
+      </c>
+      <c r="H12">
+        <v>0.1586287042417198</v>
+      </c>
+      <c r="I12">
+        <v>0.1556252502207414</v>
+      </c>
+      <c r="J12">
+        <v>0.2172974956939945</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>2966.4970286666471</v>
+        <v>2966.49702774347</v>
       </c>
       <c r="E13">
-        <v>2799.589618938297</v>
+        <v>2799.589618067062</v>
       </c>
       <c r="F13">
-        <v>-166.90740972834959</v>
+        <v>-166.9074096764075</v>
       </c>
       <c r="G13">
-        <v>-5.6264141887028843E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.0562641418870287</v>
+      </c>
+      <c r="H13">
+        <v>0.6707340693395319</v>
+      </c>
+      <c r="I13">
+        <v>0.6654009897232557</v>
+      </c>
+      <c r="J13">
+        <v>0.7749092401995692</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>800.3180821149183</v>
+        <v>800.3180821542185</v>
       </c>
       <c r="E14">
-        <v>788.86138880981366</v>
+        <v>788.8613888485513</v>
       </c>
       <c r="F14">
-        <v>-11.45669330510464</v>
+        <v>-11.45669330566716</v>
       </c>
       <c r="G14">
-        <v>-1.431517488000422E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.01431517488000414</v>
+      </c>
+      <c r="H14">
+        <v>0.4082140634723087</v>
+      </c>
+      <c r="I14">
+        <v>0.4104836703607108</v>
+      </c>
+      <c r="J14">
+        <v>0.2956548262474083</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D15">
-        <v>252.5393948137008</v>
+        <v>252.5393948261019</v>
       </c>
       <c r="E15">
-        <v>242.78330053524499</v>
+        <v>242.783300547167</v>
       </c>
       <c r="F15">
-        <v>-9.7560942784558335</v>
+        <v>-9.75609427893491</v>
       </c>
       <c r="G15">
-        <v>-3.863196981862152E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.03863196981862151</v>
+      </c>
+      <c r="H15">
+        <v>0.1288114499066581</v>
+      </c>
+      <c r="I15">
+        <v>0.126332181698427</v>
+      </c>
+      <c r="J15">
+        <v>0.2517686632551315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>907.67782483765188</v>
+        <v>907.6778248822241</v>
       </c>
       <c r="E16">
-        <v>890.14037975794622</v>
+        <v>890.1403798016572</v>
       </c>
       <c r="F16">
-        <v>-17.537445079705659</v>
+        <v>-17.53744508056684</v>
       </c>
       <c r="G16">
-        <v>-1.9321222354244941E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.01932122235424493</v>
+      </c>
+      <c r="H16">
+        <v>0.4629744866210333</v>
+      </c>
+      <c r="I16">
+        <v>0.4631841479408622</v>
+      </c>
+      <c r="J16">
+        <v>0.4525765104974602</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>6.3354054488617928</v>
+        <v>6.335405446248221</v>
       </c>
       <c r="E17">
-        <v>6.4955479050344618</v>
+        <v>6.495547902354826</v>
       </c>
       <c r="F17">
-        <v>0.16014245617266901</v>
+        <v>0.1601424561066045</v>
       </c>
       <c r="G17">
-        <v>2.5277380818845601E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.02527738081884556</v>
+      </c>
+      <c r="H17">
+        <v>0.7150284321689701</v>
+      </c>
+      <c r="I17">
+        <v>0.7220370319238562</v>
+      </c>
+      <c r="J17">
+        <v>1.179358721779985</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>0.66074780754999618</v>
+        <v>0.660747807277415</v>
       </c>
       <c r="E18">
-        <v>0.6452080125438211</v>
+        <v>0.6452080122776507</v>
       </c>
       <c r="F18">
-        <v>-1.553979500617508E-2</v>
+        <v>-0.01553979499976432</v>
       </c>
       <c r="G18">
-        <v>-2.3518496510484821E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.02351849651048473</v>
+      </c>
+      <c r="H18">
+        <v>0.07457351746547462</v>
+      </c>
+      <c r="I18">
+        <v>0.07172052075692592</v>
+      </c>
+      <c r="J18">
+        <v>-0.1144418114547029</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>1.8642013306693841</v>
+        <v>1.864201329900337</v>
       </c>
       <c r="E19">
-        <v>1.855386410090393</v>
+        <v>1.855386409324982</v>
       </c>
       <c r="F19">
-        <v>-8.8149205789918028E-3</v>
+        <v>-0.008814920575355156</v>
       </c>
       <c r="G19">
-        <v>-4.7285239174390051E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.004728523917438904</v>
+      </c>
+      <c r="H19">
+        <v>0.2103980503655554</v>
+      </c>
+      <c r="I19">
+        <v>0.2062424473192178</v>
+      </c>
+      <c r="J19">
+        <v>-0.06491691032528261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>28420.738487972219</v>
+        <v>28420.73848797222</v>
       </c>
       <c r="E20">
-        <v>29477.977713350541</v>
+        <v>29477.97771335054</v>
       </c>
       <c r="F20">
         <v>1057.239225378318</v>
       </c>
       <c r="G20">
-        <v>3.7199569104291452E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.03719956910429145</v>
+      </c>
+      <c r="H20">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="I20">
+        <v>0.1684715681373224</v>
+      </c>
+      <c r="J20">
+        <v>0.5590864708306066</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>19251.159450171741</v>
+        <v>19251.15945017174</v>
       </c>
       <c r="E21">
         <v>18859.45959321535</v>
       </c>
       <c r="F21">
-        <v>-391.69985695639122</v>
+        <v>-391.6998569563912</v>
       </c>
       <c r="G21">
-        <v>-2.0346819004342969E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.02034681900434297</v>
+      </c>
+      <c r="H21">
+        <v>0.1112256586483386</v>
+      </c>
+      <c r="I21">
+        <v>0.1077849628216685</v>
+      </c>
+      <c r="J21">
+        <v>-0.2071376897430553</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D22">
         <v>125410.102061856</v>
@@ -1004,185 +1128,242 @@
         <v>1225.472631578057</v>
       </c>
       <c r="G22">
-        <v>9.7717218264730954E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.009771721826473095</v>
+      </c>
+      <c r="H22">
+        <v>0.7245704467353974</v>
+      </c>
+      <c r="I22">
+        <v>0.7237434690410091</v>
+      </c>
+      <c r="J22">
+        <v>0.6480512189124487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D23">
         <v>19646.96893063571</v>
       </c>
       <c r="E23">
-        <v>20716.315654683149</v>
+        <v>20716.31565468315</v>
       </c>
       <c r="F23">
-        <v>1069.3467240474349</v>
+        <v>1069.346724047435</v>
       </c>
       <c r="G23">
-        <v>5.4428076301377547E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.05442807630137755</v>
+      </c>
+      <c r="H23">
+        <v>0.1703395953757214</v>
+      </c>
+      <c r="I23">
+        <v>0.1771289185151771</v>
+      </c>
+      <c r="J23">
+        <v>0.6616646788393241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24">
-        <v>60774.346098266084</v>
+        <v>60774.34609826608</v>
       </c>
       <c r="E24">
         <v>60014.07059865597</v>
       </c>
       <c r="F24">
-        <v>-760.27549961011391</v>
+        <v>-760.2754996101139</v>
       </c>
       <c r="G24">
-        <v>-1.2509809622317019E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.01250980962231702</v>
+      </c>
+      <c r="H24">
+        <v>0.5269147398843946</v>
+      </c>
+      <c r="I24">
+        <v>0.5131331071618586</v>
+      </c>
+      <c r="J24">
+        <v>-0.4704250108654359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D25">
-        <v>34918.684971098213</v>
+        <v>34918.68497109821</v>
       </c>
       <c r="E25">
-        <v>36225.759746660857</v>
+        <v>36225.75974666086</v>
       </c>
       <c r="F25">
         <v>1307.074775562643</v>
       </c>
       <c r="G25">
-        <v>3.7431958753443718E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.03743195875344372</v>
+      </c>
+      <c r="H25">
+        <v>0.3027456647398839</v>
+      </c>
+      <c r="I25">
+        <v>0.3097379743229643</v>
+      </c>
+      <c r="J25">
+        <v>0.8087603320261118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D26">
-        <v>6147.4420638390802</v>
+        <v>6147.44206383908</v>
       </c>
       <c r="E26">
         <v>6300.020290295166</v>
       </c>
       <c r="F26">
-        <v>152.57822645608579</v>
+        <v>152.5782264560858</v>
       </c>
       <c r="G26">
-        <v>2.4819790877508581E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.02481979087750858</v>
+      </c>
+      <c r="H26">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="I26">
+        <v>0.08787128903718494</v>
+      </c>
+      <c r="J26">
+        <v>0.07279481644886465</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27">
-        <v>34734.062090074352</v>
+        <v>34734.06209007435</v>
       </c>
       <c r="E27">
-        <v>35597.970774322108</v>
+        <v>35597.97077432211</v>
       </c>
       <c r="F27">
-        <v>863.90868424775545</v>
+        <v>863.9086842477554</v>
       </c>
       <c r="G27">
-        <v>2.4872089017616721E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.02487208901761672</v>
+      </c>
+      <c r="H27">
+        <v>0.4990526162367004</v>
+      </c>
+      <c r="I27">
+        <v>0.4965126197873192</v>
+      </c>
+      <c r="J27">
+        <v>0.412169387199527</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>28718.495846086571</v>
+        <v>28718.49584608657</v>
       </c>
       <c r="E28">
-        <v>29798.012935382721</v>
+        <v>29798.01293538272</v>
       </c>
       <c r="F28">
-        <v>1079.5170892961539</v>
+        <v>1079.517089296154</v>
       </c>
       <c r="G28">
-        <v>3.7589611067435427E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.03758961106743543</v>
+      </c>
+      <c r="H28">
+        <v>0.4126220667541173</v>
+      </c>
+      <c r="I28">
+        <v>0.415616091175496</v>
+      </c>
+      <c r="J28">
+        <v>0.5150357963516083</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>3914.0732538330271</v>
+        <v>3914.073253833027</v>
       </c>
       <c r="E29">
         <v>3601.574161102707</v>
       </c>
       <c r="F29">
-        <v>-312.49909273032023</v>
+        <v>-312.4990927303202</v>
       </c>
       <c r="G29">
-        <v>-7.9839868204891612E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.07983986820489161</v>
+      </c>
+      <c r="H29">
+        <v>0.08347529812606426</v>
+      </c>
+      <c r="I29">
+        <v>0.08631932144470537</v>
+      </c>
+      <c r="J29">
+        <v>0.06050142033165726</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D30">
-        <v>10643.882879045979</v>
+        <v>10643.88287904598</v>
       </c>
       <c r="E30">
-        <v>9488.0847250059651</v>
+        <v>9488.084725005965</v>
       </c>
       <c r="F30">
         <v>-1155.798154040016</v>
@@ -1190,28 +1371,43 @@
       <c r="G30">
         <v>-0.1085880187873329</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <v>0.2270017035775125</v>
+      </c>
+      <c r="I30">
+        <v>0.227401963318626</v>
+      </c>
+      <c r="J30">
+        <v>0.2237684254541961</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31">
-        <v>32331.043867120999</v>
+        <v>32331.043867121</v>
       </c>
       <c r="E31">
-        <v>28634.188113891341</v>
+        <v>28634.18811389134</v>
       </c>
       <c r="F31">
-        <v>-3696.8557532296581</v>
+        <v>-3696.855753229658</v>
       </c>
       <c r="G31">
-        <v>-0.11434384143065569</v>
+        <v>-0.1143438414306557</v>
+      </c>
+      <c r="H31">
+        <v>0.6895229982964234</v>
+      </c>
+      <c r="I31">
+        <v>0.6862787152366686</v>
+      </c>
+      <c r="J31">
+        <v>0.7157301542141465</v>
       </c>
     </row>
   </sheetData>
@@ -1220,25 +1416,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -1246,177 +1442,234 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>61551.71293278395</v>
+      </c>
+      <c r="E2">
+        <v>63378.86766281731</v>
+      </c>
+      <c r="F2">
+        <v>1827.154730033355</v>
+      </c>
+      <c r="G2">
+        <v>0.0296848721664116</v>
+      </c>
+      <c r="H2">
+        <v>0.145400609595262</v>
+      </c>
+      <c r="I2">
+        <v>0.1501277770607849</v>
+      </c>
+      <c r="J2">
+        <v>-1.576715897391229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>128642.0097639737</v>
+      </c>
+      <c r="E3">
+        <v>126884.9930305335</v>
+      </c>
+      <c r="F3">
+        <v>-1757.016733440134</v>
+      </c>
+      <c r="G3">
+        <v>-0.01365818783975644</v>
+      </c>
+      <c r="H3">
+        <v>0.3038847458179979</v>
+      </c>
+      <c r="I3">
+        <v>0.3005569939713945</v>
+      </c>
+      <c r="J3">
+        <v>1.516191360294316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>233131.2764495296</v>
+      </c>
+      <c r="E4">
+        <v>231902.3027152765</v>
+      </c>
+      <c r="F4">
+        <v>-1228.973734253057</v>
+      </c>
+      <c r="G4">
+        <v>-0.005271595270140069</v>
+      </c>
+      <c r="H4">
+        <v>0.55071464458674</v>
+      </c>
+      <c r="I4">
+        <v>0.5493152289678207</v>
+      </c>
+      <c r="J4">
+        <v>1.060524537096913</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2">
-        <v>3416.1547910068821</v>
-      </c>
-      <c r="E2">
-        <v>3276.48429544485</v>
-      </c>
-      <c r="F2">
-        <v>-139.67049556203159</v>
-      </c>
-      <c r="G2">
-        <v>-4.0885294755881069E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>28420.73848797222</v>
+      </c>
+      <c r="E5">
+        <v>29477.97771335054</v>
+      </c>
+      <c r="F5">
+        <v>1057.239225378318</v>
+      </c>
+      <c r="G5">
+        <v>0.03719956910429145</v>
+      </c>
+      <c r="H5">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="I5">
+        <v>0.1684715681373224</v>
+      </c>
+      <c r="J5">
+        <v>0.5590864708306066</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>3237.89849850784</v>
-      </c>
-      <c r="E3">
-        <v>2924.7621312353531</v>
-      </c>
-      <c r="F3">
-        <v>-313.13636727248701</v>
-      </c>
-      <c r="G3">
-        <v>-9.670975400148997E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D6">
+        <v>19251.15945017174</v>
+      </c>
+      <c r="E6">
+        <v>18859.45959321535</v>
+      </c>
+      <c r="F6">
+        <v>-391.6998569563912</v>
+      </c>
+      <c r="G6">
+        <v>-0.02034681900434297</v>
+      </c>
+      <c r="H6">
+        <v>0.1112256586483386</v>
+      </c>
+      <c r="I6">
+        <v>0.1077849628216685</v>
+      </c>
+      <c r="J6">
+        <v>-0.2071376897430553</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>11751.085501945519</v>
-      </c>
-      <c r="E4">
-        <v>10606.91183944526</v>
-      </c>
-      <c r="F4">
-        <v>-1144.173662500265</v>
-      </c>
-      <c r="G4">
-        <v>-9.7367486800332984E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D7">
+        <v>125410.102061856</v>
+      </c>
+      <c r="E7">
+        <v>126635.5746934341</v>
+      </c>
+      <c r="F7">
+        <v>1225.472631578057</v>
+      </c>
+      <c r="G7">
+        <v>0.009771721826473095</v>
+      </c>
+      <c r="H7">
+        <v>0.7245704467353974</v>
+      </c>
+      <c r="I7">
+        <v>0.7237434690410091</v>
+      </c>
+      <c r="J7">
+        <v>0.6480512189124487</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5">
-        <v>28427.073893421079</v>
-      </c>
-      <c r="E5">
-        <v>29484.473261255571</v>
-      </c>
-      <c r="F5">
-        <v>1057.3993678344921</v>
-      </c>
-      <c r="G5">
-        <v>3.7196912063439912E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>29708.48424830782</v>
+      </c>
+      <c r="E8">
+        <v>30617.91010608102</v>
+      </c>
+      <c r="F8">
+        <v>909.4258577731998</v>
+      </c>
+      <c r="G8">
+        <v>0.03061165457557802</v>
+      </c>
+      <c r="H8">
+        <v>0.128148265524623</v>
+      </c>
+      <c r="I8">
+        <v>0.1329040807410202</v>
+      </c>
+      <c r="J8">
+        <v>-0.6258939986862971</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B9" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>19251.82019797929</v>
-      </c>
-      <c r="E6">
-        <v>18860.104801227892</v>
-      </c>
-      <c r="F6">
-        <v>-391.71539675139871</v>
-      </c>
-      <c r="G6">
-        <v>-2.0346927860489469E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>125411.9662631867</v>
-      </c>
-      <c r="E7">
-        <v>126637.4300798442</v>
-      </c>
-      <c r="F7">
-        <v>1225.4638166574589</v>
-      </c>
-      <c r="G7">
-        <v>9.7715062858174783E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8">
-        <v>29708.484248307821</v>
-      </c>
-      <c r="E8">
-        <v>30617.910106081021</v>
-      </c>
-      <c r="F8">
-        <v>909.42585777319982</v>
-      </c>
-      <c r="G8">
-        <v>3.0611654575578021E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
       </c>
       <c r="D9">
         <v>106152.2910673864</v>
@@ -1425,171 +1678,228 @@
         <v>105100.126097984</v>
       </c>
       <c r="F9">
-        <v>-1052.1649694023799</v>
+        <v>-1052.16496940238</v>
       </c>
       <c r="G9">
-        <v>-9.9118441893492077E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.009911844189349208</v>
+      </c>
+      <c r="H9">
+        <v>0.4578904755979037</v>
+      </c>
+      <c r="I9">
+        <v>0.456211269692233</v>
+      </c>
+      <c r="J9">
+        <v>0.7241313124627848</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>95968.22468430577</v>
+      </c>
+      <c r="E10">
+        <v>94657.96079593492</v>
+      </c>
+      <c r="F10">
+        <v>-1310.263888370842</v>
+      </c>
+      <c r="G10">
+        <v>-0.01365310124972143</v>
+      </c>
+      <c r="H10">
+        <v>0.4139612588774733</v>
+      </c>
+      <c r="I10">
+        <v>0.4108846495667469</v>
+      </c>
+      <c r="J10">
+        <v>0.9017626862235123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10">
-        <v>95968.224684305766</v>
-      </c>
-      <c r="E10">
-        <v>94657.960795934923</v>
-      </c>
-      <c r="F10">
-        <v>-1310.2638883708421</v>
-      </c>
-      <c r="G10">
-        <v>-1.365310124972143E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>3422.490196503909</v>
+      </c>
+      <c r="E11">
+        <v>3282.979843385747</v>
+      </c>
+      <c r="F11">
+        <v>-139.5103531181626</v>
+      </c>
+      <c r="G11">
+        <v>-0.04076282037584011</v>
+      </c>
+      <c r="H11">
+        <v>0.1858634927325918</v>
+      </c>
+      <c r="I11">
+        <v>0.1952161325046486</v>
+      </c>
+      <c r="J11">
+        <v>0.08736626036831632</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>3238.559246415526</v>
+      </c>
+      <c r="E12">
+        <v>2925.407339334159</v>
+      </c>
+      <c r="F12">
+        <v>-313.1519070813665</v>
+      </c>
+      <c r="G12">
+        <v>-0.096694821139359</v>
+      </c>
+      <c r="H12">
+        <v>0.1758748450397592</v>
+      </c>
+      <c r="I12">
+        <v>0.1739537657948473</v>
+      </c>
+      <c r="J12">
+        <v>0.1961066719237173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>11752.9497033678</v>
+      </c>
+      <c r="E13">
+        <v>10608.76722590752</v>
+      </c>
+      <c r="F13">
+        <v>-1144.182477460279</v>
+      </c>
+      <c r="G13">
+        <v>-0.09735279281697382</v>
+      </c>
+      <c r="H13">
+        <v>0.6382616622276489</v>
+      </c>
+      <c r="I13">
+        <v>0.6308301017005041</v>
+      </c>
+      <c r="J13">
+        <v>0.7165270677079664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11">
-        <v>31843.228684427959</v>
-      </c>
-      <c r="E11">
-        <v>32760.957556700421</v>
-      </c>
-      <c r="F11">
-        <v>917.72887227245883</v>
-      </c>
-      <c r="G11">
-        <v>2.8820220504877651E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>31843.22868447613</v>
+      </c>
+      <c r="E14">
+        <v>32760.95755673628</v>
+      </c>
+      <c r="F14">
+        <v>917.7288722601552</v>
+      </c>
+      <c r="G14">
+        <v>0.02882022050444767</v>
+      </c>
+      <c r="H14">
+        <v>0.1662866526007706</v>
+      </c>
+      <c r="I14">
+        <v>0.1708166699586459</v>
+      </c>
+      <c r="J14">
+        <v>3.119751888634453</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12">
-        <v>22489.718696487129</v>
-      </c>
-      <c r="E12">
-        <v>21784.86693246325</v>
-      </c>
-      <c r="F12">
-        <v>-704.85176402388606</v>
-      </c>
-      <c r="G12">
-        <v>-3.1341066268382588E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D15">
+        <v>22489.71869658727</v>
+      </c>
+      <c r="E15">
+        <v>21784.86693254951</v>
+      </c>
+      <c r="F15">
+        <v>-704.8517640377613</v>
+      </c>
+      <c r="G15">
+        <v>-0.03134106626886</v>
+      </c>
+      <c r="H15">
+        <v>0.1174422379415194</v>
+      </c>
+      <c r="I15">
+        <v>0.1135869859257265</v>
+      </c>
+      <c r="J15">
+        <v>-2.396091796315172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>32</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13">
-        <v>137163.0517651322</v>
-      </c>
-      <c r="E13">
-        <v>137244.34191928941</v>
-      </c>
-      <c r="F13">
-        <v>81.290154157206416</v>
-      </c>
-      <c r="G13">
-        <v>5.9265343772316767E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14">
-        <v>61551.712932735783</v>
-      </c>
-      <c r="E14">
-        <v>63378.867662781442</v>
-      </c>
-      <c r="F14">
-        <v>1827.1547300456591</v>
-      </c>
-      <c r="G14">
-        <v>2.9684872166634721E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15">
-        <v>128642.0097638735</v>
-      </c>
-      <c r="E15">
-        <v>126884.99303044729</v>
-      </c>
-      <c r="F15">
-        <v>-1757.016733426266</v>
-      </c>
-      <c r="G15">
-        <v>-1.3658187839659259E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
       <c r="D16">
-        <v>233131.27644943801</v>
+        <v>137163.0517652238</v>
       </c>
       <c r="E16">
-        <v>231902.30271522439</v>
+        <v>137244.3419193416</v>
       </c>
       <c r="F16">
-        <v>-1228.97373421365</v>
+        <v>81.29015411777073</v>
       </c>
       <c r="G16">
-        <v>-5.2715952699731077E-3</v>
+        <v>0.0005926534374352622</v>
+      </c>
+      <c r="H16">
+        <v>0.71627110945771</v>
+      </c>
+      <c r="I16">
+        <v>0.7155963441156276</v>
+      </c>
+      <c r="J16">
+        <v>0.2763399076807183</v>
       </c>
     </row>
   </sheetData>
@@ -1598,25 +1908,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -1624,74 +1934,80 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>61551.712932735783</v>
+        <v>61551.71293278395</v>
       </c>
       <c r="E2">
-        <v>63378.867662781442</v>
+        <v>63378.86766281731</v>
       </c>
       <c r="F2">
-        <v>1827.1547300456591</v>
+        <v>1827.154730033355</v>
       </c>
       <c r="G2">
-        <v>2.9684872166634721E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.0296848721664116</v>
+      </c>
+      <c r="H2">
+        <v>-1.576715897391229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>128642.0097638735</v>
+        <v>128642.0097639737</v>
       </c>
       <c r="E3">
-        <v>126884.99303044729</v>
+        <v>126884.9930305335</v>
       </c>
       <c r="F3">
-        <v>-1757.016733426266</v>
+        <v>-1757.016733440134</v>
       </c>
       <c r="G3">
-        <v>-1.3658187839659259E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-0.01365818783975644</v>
+      </c>
+      <c r="H3">
+        <v>1.516191360294316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>233131.27644943801</v>
+        <v>233131.2764495296</v>
       </c>
       <c r="E4">
-        <v>231902.30271522439</v>
+        <v>231902.3027152765</v>
       </c>
       <c r="F4">
-        <v>-1228.97373421365</v>
+        <v>-1228.973734253057</v>
       </c>
       <c r="G4">
-        <v>-5.2715952699731077E-3</v>
+        <v>-0.005271595270140069</v>
+      </c>
+      <c r="H4">
+        <v>1.060524537096913</v>
       </c>
     </row>
   </sheetData>
